--- a/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Triphammer_20251031.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Triphammer_20251031.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,6 +686,924 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7613284</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Can - Coconut Milk</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>55.95</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>111.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4617771</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Egg Patty</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>47.08</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>564.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7456025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Egg White Patty</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>37.15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>148.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1592336</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ham (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>59.76</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>119.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5833462</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jalapenos (Sliced)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>26.69</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>80.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3656230</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nuts - Cashew Rst (Unsalted)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>189.69</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>189.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1589290</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sausage - Patty (1.5oz)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>25.75</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>257.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7143223</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sausage - Vegan Patty</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>91.20</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>182.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>9035601</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>American Cheese (Sliced)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>44.90</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>89.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1956804</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Asiago (Shredded)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>57.85</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>57.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2536555</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bacon (Pre-Cooked)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>35.95</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1078.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2916427</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Base - Chicken (No MSG)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>60.96</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>121.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8114621</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Base - Garlic</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>86.85</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>86.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5682919</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Base - Seafood</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>68.65</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>68.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>7256054</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cheddar - Orange (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>38.00</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>152.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7133036</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Chicken - Diced White &amp; Dark</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>43.75</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>437.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2393502</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>English Muffin</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>30.79</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>123.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7524051</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hot Sauce - Franks Gal</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>56.91</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>56.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4019139</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Juice - Vegetable V-8 Bulk</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4171902</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Manchego Cheese</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>84.30</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>84.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>7213975</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Potsticker - Pork &amp; Veg</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>50.95</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>50.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>7770727</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ravioli - Cheese (Med)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>43.65</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>43.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3617531</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Roasted Root Vegetables</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>60.69</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>60.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>7172870</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Salt - Kosher (Coarse)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>72.21</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>72.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4117063</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Turkey - Ground</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>59.20</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>118.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>7161191</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Vegan Mozz</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>83.95</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>167.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>7081644</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Vinegar - Sherry</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>32.55</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>32.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3335504</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Wrap - White Flour (10")</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>37.55</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>37.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1735372</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cucumber (English)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>13.91</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>27.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1094663</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Onion - Red Jumbo Fresh</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>15.95</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>15.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1094721</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Onion - Yellow Fresh</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>19.46</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>38.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>8367371</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Butternut Squash - Fresh (prepped)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>20.15</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>60.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0683696</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tomato - Fresh Sliced</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>386.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>7152564</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sweet Potato</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>20.79</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>20.79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
